--- a/timetable.xlsx
+++ b/timetable.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -710,7 +710,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -766,7 +766,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -792,7 +792,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -893,7 +893,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -4452,7 +4452,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -4552,7 +4552,7 @@
       <c r="G7" s="6" t="inlineStr"/>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -5607,25 +5607,25 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (7A)</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (7B)</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (8A)</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (8B)</t>
         </is>
       </c>
@@ -5634,7 +5634,7 @@
       <c r="H3" s="6" t="inlineStr"/>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (6A)</t>
         </is>
       </c>
@@ -5647,25 +5647,25 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (7A)</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (7B)</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (8A)</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (6A)</t>
         </is>
       </c>
@@ -5673,7 +5673,7 @@
       <c r="G4" s="6" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (6B)</t>
         </is>
       </c>
@@ -5687,38 +5687,38 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (7A)</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (7B)</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (8A)</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (8B)</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (6A)</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (6B)</t>
         </is>
       </c>
@@ -5732,25 +5732,25 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (6A)</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (7B)</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (8A)</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (8B)</t>
         </is>
       </c>
@@ -5758,7 +5758,7 @@
       <c r="G6" s="6" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (6B)</t>
         </is>
       </c>
@@ -5772,25 +5772,25 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (7A)</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (7B)</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (8A)</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (8B)</t>
         </is>
       </c>
@@ -5798,7 +5798,7 @@
       <c r="G7" s="6" t="inlineStr"/>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (6B)</t>
         </is>
       </c>
@@ -5812,27 +5812,27 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (7A)</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (6A)</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr"/>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (8B)</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr"/>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 (6B)</t>
         </is>
       </c>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -7881,7 +7881,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -8076,7 +8076,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -8196,12 +8196,12 @@
       </c>
       <c r="G2" s="10" t="inlineStr">
         <is>
+          <t>CS</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
           <t>Chemistry</t>
-        </is>
-      </c>
-      <c r="H2" s="10" t="inlineStr">
-        <is>
-          <t>ComputerScience</t>
         </is>
       </c>
       <c r="I2" s="10" t="inlineStr">
@@ -8268,10 +8268,10 @@
       <c r="F3" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="G3" s="12" t="inlineStr"/>
-      <c r="H3" s="15" t="n">
+      <c r="G3" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="H3" s="12" t="inlineStr"/>
       <c r="I3" s="16" t="n">
         <v>6</v>
       </c>
@@ -8314,10 +8314,10 @@
       <c r="F4" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="G4" s="12" t="inlineStr"/>
-      <c r="H4" s="15" t="n">
+      <c r="G4" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="H4" s="12" t="inlineStr"/>
       <c r="I4" s="16" t="n">
         <v>6</v>
       </c>
@@ -8360,10 +8360,10 @@
       <c r="F5" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="G5" s="12" t="inlineStr"/>
-      <c r="H5" s="15" t="n">
+      <c r="G5" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="H5" s="12" t="inlineStr"/>
       <c r="I5" s="16" t="n">
         <v>6</v>
       </c>
@@ -8406,10 +8406,10 @@
       <c r="F6" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="12" t="inlineStr"/>
-      <c r="H6" s="15" t="n">
+      <c r="G6" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="H6" s="12" t="inlineStr"/>
       <c r="I6" s="16" t="n">
         <v>6</v>
       </c>
@@ -8452,10 +8452,10 @@
       <c r="F7" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="12" t="inlineStr"/>
-      <c r="H7" s="15" t="n">
+      <c r="G7" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="H7" s="12" t="inlineStr"/>
       <c r="I7" s="16" t="n">
         <v>6</v>
       </c>
@@ -8498,10 +8498,10 @@
       <c r="F8" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="12" t="inlineStr"/>
-      <c r="H8" s="15" t="n">
+      <c r="G8" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="H8" s="12" t="inlineStr"/>
       <c r="I8" s="16" t="n">
         <v>6</v>
       </c>
@@ -8714,10 +8714,10 @@
       <c r="F13" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="12" t="inlineStr"/>
+      <c r="H13" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="H13" s="12" t="inlineStr"/>
       <c r="I13" s="16" t="n">
         <v>7</v>
       </c>
@@ -8756,10 +8756,10 @@
       <c r="F14" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="G14" s="12" t="inlineStr"/>
+      <c r="H14" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="H14" s="12" t="inlineStr"/>
       <c r="I14" s="16" t="n">
         <v>7</v>
       </c>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -9030,7 +9030,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -9080,7 +9080,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -9125,7 +9125,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -9316,7 +9316,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -9521,7 +9521,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -9707,7 +9707,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -9852,7 +9852,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -9902,7 +9902,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>
@@ -9957,7 +9957,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>ComputerScience
+          <t>CS
 Sanjukta</t>
         </is>
       </c>

--- a/timetable.xlsx
+++ b/timetable.xlsx
@@ -653,10 +653,10 @@
 Radheshyam</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>English
-Radheshyam</t>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>CS
+Sanjukta</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -677,188 +677,188 @@
 Snigdha</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr"/>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Pratibha</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Pratibha</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>English
+Radheshyam</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>CS
 Sanjukta</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+Ganesh</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>SST
+ANIL</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Hindi
+Snigdha</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Science
 Pratibha</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Pratibha</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Nandini</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>English
 Radheshyam</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>SST
+ANIL</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>English
+Radheshyam</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Snigdha</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Hindi
+Snigdha</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>CS
 Sanjukta</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-Ganesh</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Pratibha</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>English
+Radheshyam</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>SST
 ANIL</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Nandini</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Snigdha</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Hindi
 Snigdha</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Science
 Pratibha</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Math
 Nandini</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>English
 Radheshyam</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>SST
-ANIL</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>CS
 Sanjukta</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-Snigdha</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
-Snigdha</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>CS
-Sanjukta</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Pratibha</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>English
-Radheshyam</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>SST
-ANIL</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Nandini</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-Snigdha</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
-Snigdha</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Pratibha</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Nandini</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>English
-Radheshyam</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr"/>
       <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Odia
@@ -1034,210 +1034,210 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
+          <t>Odia
+Subhasmita</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
           <t>IT
 Usha</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>Math
 Mira</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>English
+Laxmipriya</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>Science
 Sidharth</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>English
-Laxmipriya</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sidharth</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr"/>
-    </row>
-    <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sidharth</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>IT
 Usha</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Math
 Mira</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>English
 Laxmipriya</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>English
-Laxmipriya</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sidharth</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sidharth</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>IT
 Usha</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>English
+Laxmipriya</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Math
 Mira</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>English
 Laxmipriya</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sidharth</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sidharth</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>IT
 Usha</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Math
 Mira</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="4" t="inlineStr">
         <is>
           <t>English
 Laxmipriya</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sidharth</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sidharth</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>IT
 Usha</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Math
 Mira</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sidharth</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1275,11 +1275,16 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
+          <t>Science
+Sidharth</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
           <t>Math
 Mira</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr">
         <is>
           <t>English
@@ -2807,16 +2812,16 @@
       <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Math
+(8B)</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr"/>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Math
 (9A)</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(8B)</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr"/>
       <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Math
@@ -2827,15 +2832,10 @@
       <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Math
-(9B)</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(8A)</t>
-        </is>
-      </c>
+(9A)</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr"/>
       <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
@@ -2847,27 +2847,22 @@
       <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Math
-(9A)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Math
 (8B)</t>
         </is>
       </c>
+      <c r="C4" s="6" t="inlineStr"/>
       <c r="D4" s="6" t="inlineStr"/>
       <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Math
-(9B)</t>
+(9A)</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr"/>
       <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Math
-(9A)</t>
+(9B)</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -2884,33 +2879,33 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr"/>
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Math
 (9A)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Math
 (9B)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Math
+(8B)</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Math
 (8A)</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(8B)</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr"/>
-      <c r="H5" s="6" t="inlineStr"/>
       <c r="I5" s="6" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
@@ -2919,34 +2914,39 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr"/>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Math
 (9A)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Math
 (9B)</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Math
+(9B)</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Math
+(8B)</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>Math
 (8A)</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(8B)</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr"/>
-      <c r="I6" s="6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -2957,29 +2957,29 @@
       <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Math
+(8A)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Math
 (9A)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Math
 (9B)</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(8A)</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Math
 (8B)</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr"/>
       <c r="H7" s="6" t="inlineStr"/>
       <c r="I7" s="6" t="inlineStr"/>
     </row>
@@ -2995,26 +2995,31 @@
 (8A)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Math
+(8A)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Math
 (9B)</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Math
 (9A)</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Math
 (8B)</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr"/>
       <c r="H8" s="6" t="inlineStr"/>
       <c r="I8" s="6" t="inlineStr"/>
     </row>
@@ -3127,13 +3132,13 @@
 (10B)</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>English
 (10A)</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -3153,7 +3158,7 @@
       <c r="F4" s="4" t="inlineStr">
         <is>
           <t>English
-(10B)</t>
+(7B)</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -3166,7 +3171,7 @@
       <c r="I4" s="4" t="inlineStr">
         <is>
           <t>English
-(7B)</t>
+(7A)</t>
         </is>
       </c>
     </row>
@@ -3194,20 +3199,20 @@
 (7A)</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>English
-(7A)</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>English
 (10B)</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>English
+(10B)</t>
+        </is>
+      </c>
       <c r="I5" s="6" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
@@ -3420,26 +3425,26 @@
 (12)</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Math
 (10A)</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>Math
 (10B)</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Math
 (10A)</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr"/>
       <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
@@ -3460,19 +3465,19 @@
 (12)</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Math
 (10A)</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Math
 (10B)</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr"/>
       <c r="G4" s="6" t="inlineStr"/>
       <c r="H4" s="6" t="inlineStr"/>
       <c r="I4" s="6" t="inlineStr"/>
@@ -3495,25 +3500,25 @@
 (12)</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Math
 (10A)</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Math
+(11)</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Math
 (10B)</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(11)</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr"/>
       <c r="H5" s="6" t="inlineStr"/>
       <c r="I5" s="6" t="inlineStr"/>
     </row>
@@ -3535,19 +3540,19 @@
 (12)</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Math
 (10A)</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Math
 (10B)</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Math
@@ -3575,19 +3580,19 @@
 (12)</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Math
 (10A)</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Math
 (10B)</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr"/>
       <c r="G7" s="6" t="inlineStr"/>
       <c r="H7" s="6" t="inlineStr"/>
       <c r="I7" s="6" t="inlineStr"/>
@@ -3619,16 +3624,16 @@
       <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Math
+(10A)</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Math
 (10B)</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(10A)</t>
-        </is>
-      </c>
+      <c r="G8" s="6" t="inlineStr"/>
       <c r="H8" s="6" t="inlineStr"/>
       <c r="I8" s="6" t="inlineStr"/>
     </row>
@@ -3742,7 +3747,12 @@
       </c>
       <c r="G3" s="6" t="inlineStr"/>
       <c r="H3" s="6" t="inlineStr"/>
-      <c r="I3" s="6" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Math
+(7B)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -3762,7 +3772,7 @@
       <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Math
-(7B)</t>
+(7A)</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr"/>
@@ -3770,7 +3780,7 @@
       <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Math
-(7A)</t>
+(7B)</t>
         </is>
       </c>
     </row>
@@ -3794,12 +3804,7 @@
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(7B)</t>
-        </is>
-      </c>
+      <c r="F5" s="6" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Math
@@ -4702,40 +4707,30 @@
       <c r="B3" s="4" t="inlineStr">
         <is>
           <t>English
+(9A)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>English
 (9B)</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>English
-(9B)</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>English
-(9A)</t>
-        </is>
-      </c>
+      <c r="D3" s="6" t="inlineStr"/>
       <c r="E3" s="4" t="inlineStr">
         <is>
           <t>English
-(9A)</t>
+(8A)</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr"/>
       <c r="G3" s="4" t="inlineStr">
         <is>
           <t>English
-(8A)</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>English
 (8B)</t>
         </is>
       </c>
+      <c r="H3" s="6" t="inlineStr"/>
       <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
@@ -4747,7 +4742,7 @@
       <c r="B4" s="4" t="inlineStr">
         <is>
           <t>English
-(9B)</t>
+(9A)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr"/>
@@ -4760,18 +4755,23 @@
       <c r="E4" s="4" t="inlineStr">
         <is>
           <t>English
-(8A)</t>
+(9B)</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>English
 (8B)</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>English
+(8B)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -4782,31 +4782,31 @@
       <c r="B5" s="4" t="inlineStr">
         <is>
           <t>English
+(9A)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>English
 (9B)</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>English
-(9A)</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr"/>
+      <c r="D5" s="6" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>English
+(8A)</t>
+        </is>
+      </c>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>English
-(8A)</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>English
 (8B)</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -4817,31 +4817,31 @@
       <c r="B6" s="4" t="inlineStr">
         <is>
           <t>English
+(9A)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>English
 (9B)</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>English
-(9A)</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>English
+(8A)</t>
+        </is>
+      </c>
       <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>English
-(8A)</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>English
 (8B)</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -4852,24 +4852,29 @@
       <c r="B7" s="4" t="inlineStr">
         <is>
           <t>English
+(9A)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>English
 (9B)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>English
-(9A)</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>English
 (8A)</t>
         </is>
       </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>English
+(8A)</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr"/>
       <c r="H7" s="6" t="inlineStr"/>
       <c r="I7" s="4" t="inlineStr">
         <is>
@@ -4890,26 +4895,26 @@
 (9B)</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>English
+(9B)</t>
+        </is>
+      </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
           <t>English
 (9A)</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>English
 (8A)</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>English
-(8B)</t>
-        </is>
-      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
       <c r="H8" s="6" t="inlineStr"/>
       <c r="I8" s="6" t="inlineStr"/>
     </row>
@@ -5321,12 +5326,7 @@
 (6A)</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>English
-(6A)</t>
-        </is>
-      </c>
+      <c r="E3" s="6" t="inlineStr"/>
       <c r="F3" s="6" t="inlineStr"/>
       <c r="G3" s="6" t="inlineStr"/>
       <c r="H3" s="4" t="inlineStr">
@@ -5397,7 +5397,12 @@
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>English
+(6A)</t>
+        </is>
+      </c>
       <c r="G5" s="6" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -5626,18 +5631,18 @@
       <c r="E3" s="5" t="inlineStr">
         <is>
           <t>CS
+(6A)</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>CS
 (8B)</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr"/>
       <c r="G3" s="6" t="inlineStr"/>
       <c r="H3" s="6" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(6A)</t>
-        </is>
-      </c>
+      <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -5703,133 +5708,133 @@
 (8A)</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>CS
 (8B)</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>CS
+(6B)</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>CS
 (6A)</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>CS
+(7B)</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>CS
+(8A)</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>CS
+(8B)</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>CS
 (6B)</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>CS
+(7A)</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>CS
+(7B)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>CS
+(8A)</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>CS
 (6A)</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(7B)</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(8A)</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>CS
 (8B)</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>CS
 (6B)</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>CS
 (7A)</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>CS
-(7B)</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(8A)</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
+(6A)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>CS
 (8B)</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(6B)</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(7A)</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(6A)</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(8B)</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr"/>
       <c r="G8" s="5" t="inlineStr">
         <is>
           <t>CS
@@ -5930,18 +5935,8 @@
       <c r="B3" s="6" t="inlineStr"/>
       <c r="C3" s="6" t="inlineStr"/>
       <c r="D3" s="6" t="inlineStr"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(10A)</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(10B)</t>
-        </is>
-      </c>
+      <c r="E3" s="6" t="inlineStr"/>
+      <c r="F3" s="6" t="inlineStr"/>
       <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Biology
@@ -5954,7 +5949,12 @@
 (11)</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Science
+(10B)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -5970,12 +5970,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(10A)</t>
-        </is>
-      </c>
+      <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Biology
@@ -5994,7 +5989,12 @@
 (11)</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Science
+(10A)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -6010,12 +6010,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(10A)</t>
-        </is>
-      </c>
+      <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Biology
@@ -6034,7 +6029,12 @@
 (11)</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Science
+(10A)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -6050,12 +6050,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(10A)</t>
-        </is>
-      </c>
+      <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="8" t="inlineStr">
         <is>
           <t>Biology
@@ -6068,8 +6063,18 @@
 (12)</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr"/>
-      <c r="I6" s="6" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Science
+(10A)</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Science
+(10A)</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -6085,18 +6090,8 @@
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(10A)</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(10B)</t>
-        </is>
-      </c>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Biology
@@ -6109,7 +6104,12 @@
 (11)</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Science
+(10A)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -6133,7 +6133,7 @@
       <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Science
-(10A)</t>
+(10B)</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -6908,179 +6908,214 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr"/>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(9B)</t>
+        </is>
+      </c>
       <c r="C3" s="6" t="inlineStr"/>
-      <c r="D3" s="6" t="inlineStr"/>
-      <c r="E3" s="6" t="inlineStr"/>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(10B)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Odia
 (8B)</t>
         </is>
       </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(10A)</t>
+        </is>
+      </c>
       <c r="G3" s="6" t="inlineStr"/>
       <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Odia
-(10B)</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
+(8A)</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr"/>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Odia
 (9B)</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr"/>
       <c r="C4" s="6" t="inlineStr"/>
-      <c r="D4" s="6" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(10B)</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(10A)</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(8A)</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(9A)</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(9B)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(10B)</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Odia
 (8B)</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(10A)</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(8A)</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(9A)</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(9B)</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(10B)</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Odia
 (8B)</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Odia
 (10A)</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(8A)</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(9A)</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(9B)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Odia
 (10B)</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(8B)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(10A)</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Odia
 (8A)</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr"/>
-      <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Odia
 (9A)</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(10A)</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(10B)</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(8B)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr"/>
-      <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(9B)</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(9A)</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(10A)</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(10B)</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr"/>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(9B)</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(9A)</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(10A)</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(8A)</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(8A)</t>
-        </is>
-      </c>
+      <c r="I7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -7094,19 +7129,14 @@
       <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Odia
-(9B)</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
+(8B)</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Odia
 (9A)</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(8A)</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr"/>
@@ -7200,34 +7230,34 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Science
 (8B)</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr"/>
       <c r="D3" s="6" t="inlineStr"/>
       <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Science
+(9A)</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Science
+(9B)</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Science
 (8A)</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(9B)</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(9A)</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr"/>
-      <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -7235,39 +7265,39 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Science
 (8B)</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr"/>
       <c r="D4" s="6" t="inlineStr"/>
       <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Science
+(8B)</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Science
 (9A)</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Science
 (9B)</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Science
 (8A)</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(9A)</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -7281,25 +7311,25 @@
       <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Science
+(9A)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Science
+(9A)</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Science
 (9B)</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(9B)</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Science
 (8B)</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(9A)</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -7318,31 +7348,26 @@
       <c r="B6" s="6" t="inlineStr"/>
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Science
+(9A)</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Science
+(8B)</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Science
 (9B)</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(8B)</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(9A)</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(8A)</t>
-        </is>
-      </c>
+      <c r="I6" s="6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -7350,12 +7375,7 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(8A)</t>
-        </is>
-      </c>
+      <c r="B7" s="6" t="inlineStr"/>
       <c r="C7" s="6" t="inlineStr"/>
       <c r="D7" s="6" t="inlineStr"/>
       <c r="E7" s="4" t="inlineStr">
@@ -7373,16 +7393,21 @@
       <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Science
+(9B)</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Science
 (8B)</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(8B)</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Science
+(8A)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -7392,23 +7417,23 @@
       </c>
       <c r="B8" s="6" t="inlineStr"/>
       <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Science
+(9A)</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Science
 (8A)</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Science
 (9B)</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(9A)</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr"/>
@@ -7517,198 +7542,193 @@
       <c r="D3" s="5" t="inlineStr">
         <is>
           <t>IT
+(10A)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>IT
 (10B)</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr"/>
       <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(9B)</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(11)</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr"/>
+      <c r="I3" s="6" t="inlineStr"/>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(12)</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(9A)</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>IT
 (10A)</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(10B)</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(9B)</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>IT
 (11)</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(12)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(10A)</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(10B)</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>IT
 (9B)</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr"/>
-    </row>
-    <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(11)</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>IT
 (12)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(10A)</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(10B)</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>IT
 (9A)</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(9B)</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(12)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(10A)</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>IT
 (10B)</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>IT
-(10A)</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
+(9A)</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>IT
 (11)</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>IT
-(9B)</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>IT
-(12)</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>IT
-(10B)</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>IT
-(9A)</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>IT
-(10A)</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>IT
-(11)</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>IT
-(9B)</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>IT
-(12)</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>IT
-(10B)</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>IT
-(9A)</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>IT
-(10A)</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>IT
-(9B)</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>IT
-(12)</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>IT
-(10B)</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>IT
-(10A)</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>IT
-(11)</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>IT
-(9B)</t>
-        </is>
-      </c>
+      <c r="H7" s="6" t="inlineStr"/>
       <c r="I7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
@@ -7726,7 +7746,12 @@
       <c r="C8" s="6" t="inlineStr"/>
       <c r="D8" s="6" t="inlineStr"/>
       <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(9B)</t>
+        </is>
+      </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
           <t>IT
@@ -7903,7 +7928,12 @@
 Srikant</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Nandini</t>
+        </is>
+      </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Hindi
@@ -7918,8 +7948,8 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Math
-Nandini</t>
+          <t>English
+Laxmipriya</t>
         </is>
       </c>
     </row>
@@ -7947,12 +7977,7 @@
 Laxmipriya</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>English
-Laxmipriya</t>
-        </is>
-      </c>
+      <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>SST
@@ -8467,7 +8492,7 @@
         <v>6</v>
       </c>
       <c r="M7" s="15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N7" s="12" t="inlineStr"/>
       <c r="O7" s="16" t="n">
@@ -8477,7 +8502,7 @@
         <v>4</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
@@ -8513,7 +8538,7 @@
         <v>6</v>
       </c>
       <c r="M8" s="15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N8" s="12" t="inlineStr"/>
       <c r="O8" s="16" t="n">
@@ -8557,7 +8582,7 @@
         <v>7</v>
       </c>
       <c r="M9" s="15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N9" s="12" t="inlineStr"/>
       <c r="O9" s="16" t="n">
@@ -8599,7 +8624,7 @@
         <v>7</v>
       </c>
       <c r="M10" s="15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N10" s="12" t="inlineStr"/>
       <c r="O10" s="16" t="n">
@@ -8641,7 +8666,7 @@
         <v>7</v>
       </c>
       <c r="M11" s="15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N11" s="12" t="inlineStr"/>
       <c r="O11" s="16" t="n">
@@ -8649,7 +8674,7 @@
       </c>
       <c r="P11" s="12" t="inlineStr"/>
       <c r="Q11" s="16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -8683,7 +8708,7 @@
         <v>7</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N12" s="12" t="inlineStr"/>
       <c r="O12" s="16" t="n">
@@ -8743,7 +8768,7 @@
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
@@ -8805,7 +8830,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
@@ -8815,7 +8840,7 @@
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
@@ -8959,7 +8984,12 @@
 Priyanka</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Nandini</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -8993,26 +9023,26 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
+          <t>English
+Laxmipriya</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Priyanka</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
           <t>Math
 Nandini</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Priyanka</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>English
-Laxmipriya</t>
         </is>
       </c>
     </row>
@@ -9046,12 +9076,7 @@
 Ganesh</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Nandini</t>
-        </is>
-      </c>
+      <c r="F5" s="6" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Science
@@ -9322,29 +9347,29 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>SST
+ANIL</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr"/>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Subhasmita</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
           <t>Science
 Sunil</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>SST
-ANIL</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -9370,36 +9395,31 @@
 Sanjukta</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
+      <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr">
         <is>
           <t>SST
 ANIL</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sunil</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Math
+JB</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -9427,23 +9447,28 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>SST
+ANIL</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Subhasmita</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>Math
 JB</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>SST
-ANIL</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
           <t>Science
@@ -9477,8 +9502,8 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Math
-JB</t>
+          <t>English
+Pratikshya</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -9487,17 +9512,17 @@
 ANIL</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Subhasmita</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr"/>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Science
-Sunil</t>
+          <t>Math
+JB</t>
         </is>
       </c>
     </row>
@@ -9509,8 +9534,8 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Science
-Sunil</t>
+          <t>Math
+JB</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -9527,27 +9552,27 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
           <t>English
 Pratikshya</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-Subhasmita</t>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
         </is>
       </c>
     </row>
@@ -9571,23 +9596,23 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
+          <t>Math
+JB</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
           <t>Science
 Sunil</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-Subhasmita</t>
-        </is>
-      </c>
+      <c r="G8" s="6" t="inlineStr"/>
       <c r="H8" s="7" t="inlineStr">
         <is>
           <t>CCA</t>
@@ -9689,16 +9714,16 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
+          <t>Math
+JB</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
           <t>Science
 Sunil</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
           <t>SST
@@ -9706,271 +9731,276 @@
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Subhasmita</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>CS
 Sanjukta</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr"/>
+      <c r="I3" s="6" t="inlineStr"/>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Math
+JB</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>SST
+ANIL</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Hindi
+Snigdha</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+Ganesh</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>SST
+ANIL</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>CS
+Sanjukta</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Math
+JB</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>English
 Pratikshya</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr"/>
-    </row>
-    <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sunil</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Hindi
+Snigdha</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+Ganesh</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>SST
 ANIL</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>CS
+Sanjukta</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Math
+JB</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Hindi
+Snigdha</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+Ganesh</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>SST
+ANIL</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>CS
+Sanjukta</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Math
+JB</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>English
 Pratikshya</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Hindi
 Snigdha</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Sanskrit
 Ganesh</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>SST
 ANIL</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Subhasmita</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>CS
 Sanjukta</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Math
 JB</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sunil</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-Subhasmita</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
-Snigdha</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-Ganesh</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>SST
-ANIL</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>CS
-Sanjukta</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sunil</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
-Snigdha</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-Ganesh</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>SST
-ANIL</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>CS
-Sanjukta</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sunil</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sunil</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
-Snigdha</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-Ganesh</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>SST
-ANIL</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>CS
-Sanjukta</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -10074,8 +10104,8 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Math
-JB</t>
+          <t>English
+Pratikshya</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -10086,14 +10116,14 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>English
-Pratikshya</t>
+          <t>Math
+JB</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>English
-Pratikshya</t>
+          <t>Science
+Sunil</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10104,8 +10134,8 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Science
-Sunil</t>
+          <t>Math
+JB</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -10124,8 +10154,8 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Math
-JB</t>
+          <t>English
+Pratikshya</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -10142,26 +10172,26 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
+          <t>Math
+JB</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
           <t>Science
 Sunil</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sunil</t>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Subhasmita</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr"/>
@@ -10174,168 +10204,173 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
           <t>Math
 JB</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Subhasmita</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>SST
 Srikant</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Math
+JB</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>IT
 Usha</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Math
+JB</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Science
 Sunil</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>IT
 Usha</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>IT
+Usha</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Science
 Sunil</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Math
 JB</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sunil</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>IT
-Usha</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-Subhasmita</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sunil</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -10437,18 +10472,18 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Subhasmita</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>English
 Pratikshya</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
           <t>SST
@@ -10461,74 +10496,69 @@
 JB</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sunil</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>IT
 Usha</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr"/>
+      <c r="I3" s="6" t="inlineStr"/>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>English
 Pratikshya</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sunil</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>IT
 Usha</t>
         </is>
       </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Math
+JB</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
       <c r="I4" s="6" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
@@ -10537,43 +10567,43 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Subhasmita</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>English
 Pratikshya</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Math
 JB</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sunil</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sunil</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>IT
 Usha</t>
         </is>
       </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr"/>
       <c r="I5" s="6" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
@@ -10582,43 +10612,48 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Math
+JB</t>
+        </is>
+      </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Science
-Sunil</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr">
+          <t>Math
+JB</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>IT
 Usha</t>
         </is>
       </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
       <c r="I6" s="6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
@@ -10627,82 +10662,87 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Math
+JB</t>
+        </is>
+      </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Science
 Sunil</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Math
+JB</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>IT
 Usha</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-Subhasmita</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Science
 Sunil</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr"/>
       <c r="H8" s="7" t="inlineStr">
         <is>
           <t>CCA</t>
@@ -10814,37 +10854,37 @@
 ANIL</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Mira</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sidharth</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>IT
 Usha</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Math
 Mira</t>
         </is>
       </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Subhasmita</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr"/>
       <c r="H3" s="4" t="inlineStr">
         <is>
+          <t>Math
+Mira</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
           <t>English
 Laxmipriya</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -10864,32 +10904,32 @@
 Laxmipriya</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Mira</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sidharth</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>IT
 Usha</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Mira</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
+      <c r="G4" s="6" t="inlineStr"/>
       <c r="H4" s="6" t="inlineStr"/>
-      <c r="I4" s="6" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sidharth</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -10909,32 +10949,32 @@
 Laxmipriya</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Mira</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sidharth</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>IT
 Usha</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Mira</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
+      <c r="G5" s="6" t="inlineStr"/>
       <c r="H5" s="6" t="inlineStr"/>
-      <c r="I5" s="6" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sidharth</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -10954,32 +10994,37 @@
 Laxmipriya</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Mira</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sidharth</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>IT
 Usha</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Mira</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr"/>
-      <c r="I6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sidharth</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sidharth</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -10999,32 +11044,32 @@
 Laxmipriya</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Mira</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sidharth</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>IT
 Usha</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Mira</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
+      <c r="G7" s="6" t="inlineStr"/>
       <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sidharth</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -11052,8 +11097,8 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Science
-Sidharth</t>
+          <t>Math
+Mira</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -11062,12 +11107,7 @@
 Laxmipriya</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Mira</t>
-        </is>
-      </c>
+      <c r="G8" s="6" t="inlineStr"/>
       <c r="H8" s="7" t="inlineStr">
         <is>
           <t>CCA</t>

--- a/timetable.xlsx
+++ b/timetable.xlsx
@@ -641,284 +641,284 @@
 Pratibha</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Hindi
+Snigdha</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+Ganesh</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>English
+Radheshyam</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>Math
 Nandini</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>English
-Radheshyam</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>SST
+ANIL</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Snigdha</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>CS
 Sanjukta</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Pratibha</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Nandini</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>English
+Radheshyam</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Nandini</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>CS
+Sanjukta</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>SST
+ANIL</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Snigdha</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Pratibha</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Sanskrit
 Ganesh</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>English
+Radheshyam</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Nandini</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>SST
 ANIL</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Hindi
 Snigdha</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr"/>
-    </row>
-    <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Snigdha</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Science
 Pratibha</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+Ganesh</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>English
+Radheshyam</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Nandini</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>SST
+ANIL</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Hindi
+Snigdha</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Snigdha</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Science
 Pratibha</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Nandini</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>English
 Radheshyam</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>CS
 Sanjukta</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>SST
+ANIL</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Snigdha</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Sanskrit
 Ganesh</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>SST
-ANIL</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Pratibha</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>English
+Radheshyam</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>CS
+Sanjukta</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Hindi
 Snigdha</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Pratibha</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Nandini</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>English
-Radheshyam</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>SST
 ANIL</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>English
-Radheshyam</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-Snigdha</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
-Snigdha</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>CS
-Sanjukta</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Pratibha</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>English
-Radheshyam</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>SST
-ANIL</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Nandini</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-Snigdha</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
-Snigdha</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Pratibha</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Nandini</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>English
-Radheshyam</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>CS
-Sanjukta</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-Snigdha</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-Ganesh</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>SST
-ANIL</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Nandini</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>CS
-Sanjukta</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Nandini</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>SST
-ANIL</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-Snigdha</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-Ganesh</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -1020,24 +1020,24 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
           <t>IT
@@ -1070,30 +1070,30 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sidharth</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>IT
 Usha</t>
         </is>
       </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>IT
+Usha</t>
+        </is>
+      </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Math
@@ -1107,7 +1107,12 @@
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr"/>
-      <c r="I4" s="6" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sidharth</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -1115,24 +1120,24 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sidharth</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Mira</t>
+        </is>
+      </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
           <t>IT
@@ -1141,23 +1146,23 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
+          <t>Math
+Mira</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
           <t>English
 Laxmipriya</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Mira</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>English
-Laxmipriya</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sidharth</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -1165,24 +1170,24 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sidharth</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Mira</t>
+        </is>
+      </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
           <t>IT
@@ -1191,8 +1196,8 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Math
-Mira</t>
+          <t>English
+Laxmipriya</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -1201,8 +1206,18 @@
 Laxmipriya</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr"/>
-      <c r="I6" s="6" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sidharth</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sidharth</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -1210,24 +1225,24 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sidharth</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Mira</t>
+        </is>
+      </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
           <t>IT
@@ -1236,8 +1251,8 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Math
-Mira</t>
+          <t>Science
+Sidharth</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1247,7 +1262,12 @@
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sidharth</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -1255,36 +1275,31 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Subhasmita</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>SST
 Srikant</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sidharth</t>
-        </is>
-      </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Math
 Mira</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sidharth</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Mira</t>
-        </is>
-      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>IT
+Usha</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr">
         <is>
           <t>English
@@ -1398,8 +1413,8 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>English
-Radheshyam</t>
+          <t>Math
+Mira</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
@@ -1514,25 +1529,30 @@
 Pratibha</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Mira</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>IT
 Usha</t>
         </is>
       </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>IT
+Usha</t>
+        </is>
+      </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
           <t>Biology
 Sidharth</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>English
+Radheshyam</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -1570,10 +1590,10 @@
 Sidharth</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Mira</t>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>IT
+Usha</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr"/>
@@ -1627,7 +1647,12 @@
 Sidharth</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>English
+Radheshyam</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -1637,8 +1662,8 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>English
-Radheshyam</t>
+          <t>Math
+Mira</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -1776,10 +1801,10 @@
 Usha</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Mira</t>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>IT
+Usha</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
@@ -1808,11 +1833,16 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
+          <t>Math
+Mira</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
           <t>English
 Radheshyam</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -1858,11 +1888,16 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
+          <t>Math
+Mira</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
           <t>English
 Radheshyam</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -2015,10 +2050,10 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Mira</t>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>IT
+Usha</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -2168,13 +2203,13 @@
 (8B)</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>SST
 (8A)</t>
         </is>
       </c>
+      <c r="F3" s="6" t="inlineStr"/>
       <c r="G3" s="4" t="inlineStr">
         <is>
           <t>SST
@@ -2213,13 +2248,13 @@
 (8B)</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>SST
 (8A)</t>
         </is>
       </c>
+      <c r="F4" s="6" t="inlineStr"/>
       <c r="G4" s="4" t="inlineStr">
         <is>
           <t>SST
@@ -2250,19 +2285,19 @@
       <c r="D5" s="4" t="inlineStr">
         <is>
           <t>SST
+(8A)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>SST
 (8B)</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>SST
 (6A)</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>SST
-(8A)</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr"/>
@@ -2290,19 +2325,19 @@
       <c r="D6" s="4" t="inlineStr">
         <is>
           <t>SST
+(8A)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>SST
 (8B)</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>SST
 (6A)</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>SST
-(8A)</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr"/>
@@ -2324,29 +2359,29 @@
       <c r="C7" s="4" t="inlineStr">
         <is>
           <t>SST
+(6B)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>SST
 (8A)</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>SST
 (8B)</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>SST
-(6B)</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>SST
 (6A)</t>
         </is>
       </c>
+      <c r="H7" s="6" t="inlineStr"/>
       <c r="I7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
@@ -2364,28 +2399,28 @@
       <c r="C8" s="4" t="inlineStr">
         <is>
           <t>SST
+(6B)</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>SST
 (8A)</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>SST
 (8B)</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>SST
 (6A)</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>SST
-(6B)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr"/>
       <c r="H8" s="6" t="inlineStr"/>
       <c r="I8" s="6" t="inlineStr"/>
     </row>
@@ -2491,233 +2526,243 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
+          <t>Sanskrit
+(6A)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+(7B)</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>Odia
 (7A)</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+(6B)</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+(7A)</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr"/>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(7B)</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+(8A)</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Sanskrit
 (7B)</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(7A)</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+(6B)</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+(7A)</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(7B)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Sanskrit
 (6A)</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+(8B)</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+(7B)</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(7A)</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Sanskrit
 (6B)</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Sanskrit
 (7A)</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr"/>
-    </row>
-    <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Odia
 (7B)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+(6A)</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+(8B)</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+(7B)</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+(6B)</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(7B)</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Sanskrit
 (8A)</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+(8B)</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Odia
 (7A)</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Sanskrit
-(7B)</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
+(7A)</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Sanskrit
 (6A)</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-(6B)</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-(7A)</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Sanskrit
 (8A)</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Sanskrit
 (8B)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-(7B)</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-(6B)</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-(7A)</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-(8A)</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-(8B)</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-(7B)</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-(6B)</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr"/>
-      <c r="I6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(7B)</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-(8B)</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Odia
 (7A)</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-(6A)</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-(7A)</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(7B)</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-(8B)</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(7A)</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-(6A)</t>
-        </is>
-      </c>
+      <c r="G8" s="6" t="inlineStr"/>
       <c r="H8" s="6" t="inlineStr"/>
       <c r="I8" s="6" t="inlineStr"/>
     </row>
@@ -2815,28 +2860,33 @@
 (8B)</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Math
+(9A)</t>
+        </is>
+      </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Math
+(8A)</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Math
 (9A)</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr"/>
+      <c r="H3" s="6" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>Math
 (9B)</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(9A)</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr"/>
-      <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -2850,27 +2900,27 @@
 (8B)</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr"/>
-      <c r="D4" s="6" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Math
+(9A)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Math
+(8A)</t>
+        </is>
+      </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Math
-(9A)</t>
+(9B)</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(9B)</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(8A)</t>
-        </is>
-      </c>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
       <c r="I4" s="6" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
@@ -2879,31 +2929,36 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr"/>
-      <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Math
+(8A)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Math
 (9A)</t>
         </is>
       </c>
+      <c r="D5" s="6" t="inlineStr"/>
       <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Math
 (9B)</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Math
+(9B)</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Math
 (8B)</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(8A)</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr"/>
@@ -2914,24 +2969,24 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Math
+(8A)</t>
+        </is>
+      </c>
       <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Math
+(9B)</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Math
 (9A)</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(9B)</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(9B)</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr"/>
@@ -2941,12 +2996,7 @@
 (8B)</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(8A)</t>
-        </is>
-      </c>
+      <c r="I6" s="6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -2960,13 +3010,13 @@
 (8A)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Math
 (9A)</t>
         </is>
       </c>
+      <c r="D7" s="6" t="inlineStr"/>
       <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Math
@@ -2996,12 +3046,7 @@
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(8A)</t>
-        </is>
-      </c>
+      <c r="D8" s="6" t="inlineStr"/>
       <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Math
@@ -3111,34 +3156,34 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr"/>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>English
+(7A)</t>
+        </is>
+      </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
           <t>English
-(7A)</t>
+(7B)</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr"/>
       <c r="E3" s="6" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>English
-(7B)</t>
-        </is>
-      </c>
+      <c r="F3" s="6" t="inlineStr"/>
       <c r="G3" s="4" t="inlineStr">
         <is>
           <t>English
 (10B)</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr"/>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>English
 (10A)</t>
         </is>
       </c>
+      <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -3146,11 +3191,16 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>English
+(7A)</t>
+        </is>
+      </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
           <t>English
-(10A)</t>
+(7B)</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr"/>
@@ -3158,7 +3208,7 @@
       <c r="F4" s="4" t="inlineStr">
         <is>
           <t>English
-(7B)</t>
+(10A)</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -3167,13 +3217,13 @@
 (10B)</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>English
-(7A)</t>
-        </is>
-      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>English
+(10A)</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -3184,36 +3234,36 @@
       <c r="B5" s="4" t="inlineStr">
         <is>
           <t>English
+(7A)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>English
 (7B)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>English
-(10A)</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>English
-(7A)</t>
-        </is>
-      </c>
+      <c r="D5" s="6" t="inlineStr"/>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>English
+(10A)</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>English
 (10B)</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>English
-(10B)</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>English
+(10A)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -3224,30 +3274,35 @@
       <c r="B6" s="4" t="inlineStr">
         <is>
           <t>English
+(7A)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>English
 (7B)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>English
+(10B)</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>English
+(10B)</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>English
 (10A)</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>English
-(7A)</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>English
-(10B)</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr"/>
       <c r="I6" s="6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
@@ -3256,25 +3311,20 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr"/>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>English
+(7A)</t>
+        </is>
+      </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
           <t>English
-(10A)</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>English
-(7A)</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>English
 (7B)</t>
         </is>
       </c>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
       <c r="F7" s="6" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr">
         <is>
@@ -3282,7 +3332,12 @@
 (10B)</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>English
+(10A)</t>
+        </is>
+      </c>
       <c r="I7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
@@ -3291,31 +3346,21 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr"/>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>English
+(7A)</t>
+        </is>
+      </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
           <t>English
-(10A)</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>English
-(7A)</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>English
 (7B)</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>English
-(10A)</t>
-        </is>
-      </c>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr">
         <is>
           <t>English
@@ -3422,27 +3467,27 @@
       <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Math
+(11)</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr"/>
+      <c r="E3" s="6" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Math
+(10B)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Math
+(10A)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Math
 (12)</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(10A)</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(10B)</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(10A)</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr"/>
@@ -3465,21 +3510,31 @@
 (12)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Math
 (10A)</t>
         </is>
       </c>
+      <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Math
 (10B)</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr"/>
-      <c r="H4" s="6" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Math
+(10A)</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Math
+(12)</t>
+        </is>
+      </c>
       <c r="I4" s="6" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
@@ -3500,26 +3555,26 @@
 (12)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Math
+(10B)</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Math
+(10B)</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Math
 (10A)</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(11)</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(10B)</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr"/>
       <c r="I5" s="6" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
@@ -3540,25 +3595,20 @@
 (12)</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Math
+(10B)</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Math
 (10A)</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(10B)</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(11)</t>
-        </is>
-      </c>
+      <c r="G6" s="6" t="inlineStr"/>
       <c r="H6" s="6" t="inlineStr"/>
       <c r="I6" s="6" t="inlineStr"/>
     </row>
@@ -3580,17 +3630,17 @@
 (12)</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Math
+(10B)</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Math
 (10A)</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(10B)</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr"/>
@@ -3606,31 +3656,26 @@
       <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Math
+(11)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Math
 (12)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(12)</t>
-        </is>
-      </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Math
 (10B)</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Math
 (10A)</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(10B)</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr"/>
@@ -3726,31 +3771,31 @@
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr"/>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(6A)</t>
-        </is>
-      </c>
+      <c r="C3" s="6" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Math
-(6B)</t>
+(7A)</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>Math
-(7A)</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr"/>
+(6A)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Math
+(7B)</t>
+        </is>
+      </c>
       <c r="H3" s="6" t="inlineStr"/>
       <c r="I3" s="4" t="inlineStr">
         <is>
           <t>Math
-(7B)</t>
+(6B)</t>
         </is>
       </c>
     </row>
@@ -3761,18 +3806,28 @@
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr"/>
-      <c r="C4" s="6" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Math
+(6A)</t>
+        </is>
+      </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Math
-(6B)</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr"/>
+(7A)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Math
+(6A)</t>
+        </is>
+      </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Math
-(7A)</t>
+(7B)</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr"/>
@@ -3780,7 +3835,7 @@
       <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Math
-(7B)</t>
+(6B)</t>
         </is>
       </c>
     </row>
@@ -3791,19 +3846,19 @@
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr"/>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Math
+(7B)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Math
 (6A)</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(7B)</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
@@ -3812,7 +3867,12 @@
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr"/>
-      <c r="I5" s="6" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Math
+(6B)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -3828,13 +3888,13 @@
 (7B)</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Math
 (6A)</t>
         </is>
       </c>
+      <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Math
@@ -3865,29 +3925,24 @@
       <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Math
+(7A)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Math
+(7B)</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Math
 (6B)</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(6B)</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(7B)</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr"/>
       <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(7A)</t>
-        </is>
-      </c>
+      <c r="I7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -3895,34 +3950,24 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(6A)</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Math
 (7A)</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(6A)</t>
-        </is>
-      </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Math
+(7B)</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Math
 (6B)</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Math
-(7B)</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr"/>
@@ -4063,12 +4108,7 @@
 (6A)</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(6A)</t>
-        </is>
-      </c>
+      <c r="C4" s="6" t="inlineStr"/>
       <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Physics
@@ -4083,13 +4123,13 @@
       </c>
       <c r="F4" s="6" t="inlineStr"/>
       <c r="G4" s="6" t="inlineStr"/>
-      <c r="H4" s="6" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Science
 (6B)</t>
         </is>
       </c>
+      <c r="I4" s="6" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -4118,13 +4158,13 @@
       </c>
       <c r="F5" s="6" t="inlineStr"/>
       <c r="G5" s="6" t="inlineStr"/>
-      <c r="H5" s="6" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Science
 (6B)</t>
         </is>
       </c>
+      <c r="I5" s="6" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -4132,13 +4172,13 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Science
 (6A)</t>
         </is>
       </c>
+      <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Physics
@@ -4153,7 +4193,12 @@
       </c>
       <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="6" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Science
+(6B)</t>
+        </is>
+      </c>
       <c r="I6" s="6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
@@ -4168,12 +4213,7 @@
 (6A)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(6B)</t>
-        </is>
-      </c>
+      <c r="C7" s="6" t="inlineStr"/>
       <c r="D7" s="8" t="inlineStr">
         <is>
           <t>Physics
@@ -4193,7 +4233,12 @@
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Science
+(6B)</t>
+        </is>
+      </c>
       <c r="I7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
@@ -4202,16 +4247,11 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(6B)</t>
-        </is>
-      </c>
+      <c r="B8" s="6" t="inlineStr"/>
       <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Science
-(6B)</t>
+(6A)</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -4227,7 +4267,12 @@
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Science
+(6B)</t>
+        </is>
+      </c>
       <c r="H8" s="6" t="inlineStr"/>
       <c r="I8" s="6" t="inlineStr"/>
     </row>
@@ -4331,278 +4376,278 @@
 Pratibha</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Nandini</t>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>CS
+Sanjukta</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Hindi
+Snigdha</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Odia
 Snigdha</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+Ganesh</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>SST
+ANIL</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Nandini</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>English
+Radheshyam</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>SST
+ANIL</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>CS
+Sanjukta</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Hindi
 Snigdha</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Snigdha</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Sanskrit
 Ganesh</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Pratibha</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Nandini</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>English
+Radheshyam</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>SST
 ANIL</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr"/>
-    </row>
-    <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>English
-Radheshyam</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>SST
-ANIL</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Nandini</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Hindi
+Snigdha</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Odia
 Snigdha</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+Ganesh</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Pratibha</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Nandini</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>English
+Radheshyam</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>SST
+ANIL</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Hindi
 Snigdha</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Snigdha</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Sanskrit
 Ganesh</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Pratibha</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Nandini</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>English
+Radheshyam</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>SST
+ANIL</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>CS
 Sanjukta</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Pratibha</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>English
-Radheshyam</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>SST
-ANIL</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Odia
 Snigdha</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
-Snigdha</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-Ganesh</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Nandini</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Pratibha</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>English
+Radheshyam</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>SST
+ANIL</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>CS
 Sanjukta</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Nandini</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Science
 Pratibha</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>English
-Radheshyam</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>SST
-ANIL</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-Snigdha</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
-Snigdha</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-Ganesh</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>CS
-Sanjukta</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Nandini</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>English
-Radheshyam</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Pratibha</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Nandini</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Nandini</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>SST
-ANIL</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>CS
-Sanjukta</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Pratibha</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Pratibha</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>English
-Radheshyam</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Nandini</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>SST
-ANIL</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>CS
-Sanjukta</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -4716,11 +4761,16 @@
 (9B)</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr"/>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>English
+(9A)</t>
+        </is>
+      </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
           <t>English
-(8A)</t>
+(9B)</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr"/>
@@ -4730,7 +4780,12 @@
 (8B)</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>English
+(8A)</t>
+        </is>
+      </c>
       <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
@@ -4745,33 +4800,33 @@
 (9A)</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>English
-(9A)</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>English
 (9B)</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>English
+(8B)</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
           <t>English
 (8B)</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>English
-(8B)</t>
-        </is>
-      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>English
+(8A)</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -4799,14 +4854,14 @@
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>English
+(8B)</t>
+        </is>
+      </c>
       <c r="H5" s="6" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>English
-(8B)</t>
-        </is>
-      </c>
+      <c r="I5" s="6" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -4834,14 +4889,14 @@
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>English
+(8B)</t>
+        </is>
+      </c>
       <c r="H6" s="6" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>English
-(8B)</t>
-        </is>
-      </c>
+      <c r="I6" s="6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -4868,20 +4923,15 @@
 (8A)</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>English
-(8A)</t>
-        </is>
-      </c>
+      <c r="F7" s="6" t="inlineStr"/>
       <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>English
 (8B)</t>
         </is>
       </c>
+      <c r="I7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -4892,21 +4942,16 @@
       <c r="B8" s="4" t="inlineStr">
         <is>
           <t>English
+(9A)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>English
 (9B)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>English
-(9B)</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>English
-(9A)</t>
-        </is>
-      </c>
+      <c r="D8" s="6" t="inlineStr"/>
       <c r="E8" s="4" t="inlineStr">
         <is>
           <t>English
@@ -5007,7 +5052,12 @@
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr"/>
-      <c r="C3" s="6" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Science
+(7A)</t>
+        </is>
+      </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
           <t>Chemistry
@@ -5033,12 +5083,7 @@
 (7B)</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(7A)</t>
-        </is>
-      </c>
+      <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -5071,13 +5116,13 @@
 (12)</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Science
 (7B)</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr"/>
       <c r="I4" s="6" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
@@ -5106,13 +5151,13 @@
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Science
 (7B)</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr"/>
       <c r="I5" s="6" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
@@ -5121,12 +5166,7 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(7A)</t>
-        </is>
-      </c>
+      <c r="B6" s="6" t="inlineStr"/>
       <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Science
@@ -5146,13 +5186,13 @@
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Science
 (7B)</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr"/>
       <c r="I6" s="6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
@@ -5181,13 +5221,13 @@
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>Science
 (7B)</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr"/>
       <c r="I7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
@@ -5196,11 +5236,16 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr"/>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Science
+(7B)</t>
+        </is>
+      </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Science
-(7B)</t>
+(7A)</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -5314,28 +5359,23 @@
 (6B)</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>English
-(11)</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr"/>
+      <c r="D3" s="6" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>English
 (6A)</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr"/>
       <c r="F3" s="6" t="inlineStr"/>
       <c r="G3" s="6" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>English
 (12)</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -5364,13 +5404,13 @@
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
       <c r="G4" s="6" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>English
 (12)</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -5397,12 +5437,7 @@
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>English
-(6A)</t>
-        </is>
-      </c>
+      <c r="F5" s="6" t="inlineStr"/>
       <c r="G5" s="6" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -5410,7 +5445,12 @@
 (12)</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>English
+(11)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -5485,7 +5525,12 @@
 (12)</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>English
+(11)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -5496,19 +5541,19 @@
       <c r="B8" s="4" t="inlineStr">
         <is>
           <t>English
+(6B)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>English
 (11)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>English
-(11)</t>
-        </is>
-      </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
           <t>English
-(6B)</t>
+(6A)</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr"/>
@@ -5610,237 +5655,207 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr"/>
+      <c r="C3" s="6" t="inlineStr"/>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>CS
+(6B)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>CS
 (7A)</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>CS
+(8B)</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr"/>
+      <c r="H3" s="6" t="inlineStr"/>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>CS
+(6A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>CS
+(6B)</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>CS
+(8B)</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>CS
+(6A)</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>CS
+(8A)</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr"/>
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>CS
+(7A)</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>CS
 (7B)</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>CS
 (8A)</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>CS
+(8B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr"/>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>CS
+(7A)</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>CS
+(7B)</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>CS
+(8A)</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>CS
+(8B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>CS
+(6B)</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>CS
 (6A)</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>CS
-(8B)</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr"/>
-      <c r="H3" s="6" t="inlineStr"/>
-      <c r="I3" s="6" t="inlineStr"/>
-    </row>
-    <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
+(7B)</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>CS
+(8A)</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>CS
 (7A)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>CS
+(6B)</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>CS
+(6A)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>CS
 (7B)</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(8A)</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(6A)</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(6B)</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(7A)</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(7B)</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(8A)</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(8B)</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(6B)</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(6A)</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(7B)</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(8A)</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(8B)</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(6B)</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(7A)</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(7B)</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(8A)</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(6A)</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(8B)</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(6B)</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(7A)</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(6A)</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(8B)</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>CS
-(6B)</t>
-        </is>
-      </c>
+      <c r="G8" s="6" t="inlineStr"/>
       <c r="H8" s="6" t="inlineStr"/>
       <c r="I8" s="6" t="inlineStr"/>
     </row>
@@ -5936,7 +5951,12 @@
       <c r="C3" s="6" t="inlineStr"/>
       <c r="D3" s="6" t="inlineStr"/>
       <c r="E3" s="6" t="inlineStr"/>
-      <c r="F3" s="6" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Science
+(10A)</t>
+        </is>
+      </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Biology
@@ -5963,12 +5983,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(10B)</t>
-        </is>
-      </c>
+      <c r="C4" s="6" t="inlineStr"/>
       <c r="D4" s="6" t="inlineStr"/>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="8" t="inlineStr">
@@ -5992,7 +6007,7 @@
       <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Science
-(10A)</t>
+(10B)</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6018,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr"/>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(10B)</t>
-        </is>
-      </c>
+      <c r="C5" s="6" t="inlineStr"/>
       <c r="D5" s="6" t="inlineStr"/>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="8" t="inlineStr">
@@ -6032,7 +6042,7 @@
       <c r="I5" s="4" t="inlineStr">
         <is>
           <t>Science
-(10A)</t>
+(10B)</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6056,7 @@
       <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Science
-(10B)</t>
+(10A)</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr"/>
@@ -6066,13 +6076,13 @@
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Science
-(10A)</t>
+(10B)</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
           <t>Science
-(10A)</t>
+(10B)</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6096,17 @@
       <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Science
-(10B)</t>
+(10A)</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr"/>
       <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Science
+(10B)</t>
+        </is>
+      </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Biology
@@ -6107,7 +6122,7 @@
       <c r="I7" s="4" t="inlineStr">
         <is>
           <t>Science
-(10A)</t>
+(10B)</t>
         </is>
       </c>
     </row>
@@ -6121,21 +6136,11 @@
       <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Science
-(10B)</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Science
 (10A)</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(10B)</t>
-        </is>
-      </c>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
       <c r="F8" s="8" t="inlineStr">
         <is>
           <t>Biology
@@ -6245,7 +6250,12 @@
 (8A)</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr"/>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Hindi
+(6A)</t>
+        </is>
+      </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Hindi
@@ -6254,223 +6264,228 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>Hindi
+(6B)</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>Odia
 (6B)</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Hindi
+(7A)</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(6A)</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr"/>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Hindi
+(8A)</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Hindi
+(7B)</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Hindi
 (6B)</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(6B)</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Hindi
 (7A)</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(6A)</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Hindi
+(8B)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Hindi
+(8A)</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Hindi
+(6B)</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(6B)</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Hindi
 (6A)</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr"/>
-    </row>
-    <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(6A)</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Hindi
+(8B)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Hindi
 (8A)</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Hindi
+(6B)</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(6B)</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Hindi
+(6A)</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(6A)</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Hindi
+(8B)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Hindi
 (7B)</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Odia
 (6B)</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
-(6B)</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Hindi
 (7A)</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Odia
 (6A)</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Hindi
 (8B)</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
-(8A)</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(6B)</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
-(6B)</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(6A)</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
-(6A)</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
-(8B)</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
-(8A)</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(6B)</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
-(6B)</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(6A)</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
-(6A)</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
-(8B)</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Hindi
 (7B)</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(6A)</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
-(7A)</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
-(8B)</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
-(7B)</t>
-        </is>
-      </c>
       <c r="E8" s="6" t="inlineStr"/>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Odia
+          <t>Hindi
 (6A)</t>
         </is>
       </c>
@@ -6574,45 +6589,40 @@
       <c r="B3" s="4" t="inlineStr">
         <is>
           <t>SST
+(9B)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>SST
 (10B)</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>SST
 (10B)</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>SST
+(9A)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>SST
+(7B)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>SST
 (9B)</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>SST
-(7A)</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>SST
-(9A)</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>SST
-(7B)</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>SST
-(9A)</t>
-        </is>
-      </c>
+      <c r="H3" s="6" t="inlineStr"/>
       <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
@@ -6624,41 +6634,41 @@
       <c r="B4" s="4" t="inlineStr">
         <is>
           <t>SST
+(9B)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>SST
 (10B)</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>SST
-(9B)</t>
-        </is>
-      </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
           <t>SST
-(9B)</t>
+(9A)</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
           <t>SST
+(9A)</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>SST
+(7B)</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>SST
 (7A)</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>SST
-(9A)</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>SST
-(7B)</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -6669,35 +6679,35 @@
       <c r="B5" s="4" t="inlineStr">
         <is>
           <t>SST
+(9B)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>SST
 (10B)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>SST
 (9A)</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>SST
-(9B)</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>SST
 (7A)</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>SST
 (7B)</t>
         </is>
       </c>
+      <c r="H5" s="6" t="inlineStr"/>
       <c r="I5" s="6" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
@@ -6709,35 +6719,40 @@
       <c r="B6" s="4" t="inlineStr">
         <is>
           <t>SST
+(9B)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>SST
 (10B)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>SST
 (9A)</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>SST
-(9B)</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>SST
+(7A)</t>
+        </is>
+      </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
           <t>SST
 (7A)</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>SST
 (7B)</t>
         </is>
       </c>
+      <c r="H6" s="6" t="inlineStr"/>
       <c r="I6" s="6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
@@ -6749,35 +6764,35 @@
       <c r="B7" s="4" t="inlineStr">
         <is>
           <t>SST
+(9B)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>SST
 (10B)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>SST
 (9A)</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>SST
-(9B)</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>SST
 (7A)</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>SST
 (7B)</t>
         </is>
       </c>
+      <c r="H7" s="6" t="inlineStr"/>
       <c r="I7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
@@ -6789,28 +6804,28 @@
       <c r="B8" s="4" t="inlineStr">
         <is>
           <t>SST
+(9B)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>SST
 (10B)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>SST
 (9A)</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>SST
-(9B)</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>SST
 (7A)</t>
         </is>
       </c>
+      <c r="F8" s="6" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr">
         <is>
           <t>SST
@@ -6911,225 +6926,245 @@
       <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Odia
+(10B)</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(8B)</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Odia
 (9B)</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr"/>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(10A)</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(8A)</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(9A)</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr"/>
+      <c r="I3" s="6" t="inlineStr"/>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Odia
 (10B)</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(9B)</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(10A)</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(8A)</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(9A)</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(10B)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Odia
 (8B)</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(9B)</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Odia
 (10A)</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Odia
 (8A)</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr"/>
-    </row>
-    <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(9A)</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(10B)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(8B)</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Odia
 (9B)</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(10A)</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(8A)</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(9A)</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Odia
 (10B)</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(8B)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(9B)</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Odia
 (10A)</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Odia
 (8A)</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Odia
 (9A)</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(10B)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+(8B)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Odia
 (9B)</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(10B)</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(8B)</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Odia
 (10A)</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(8A)</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(9A)</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(9B)</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(10B)</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(8B)</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(10A)</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(8A)</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(9A)</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(9B)</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(10B)</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(8B)</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(10A)</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(8A)</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(9A)</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr"/>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-(8B)</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr"/>
@@ -7231,33 +7266,28 @@
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr"/>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(8B)</t>
-        </is>
-      </c>
+      <c r="C3" s="6" t="inlineStr"/>
       <c r="D3" s="6" t="inlineStr"/>
       <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Science
-(9A)</t>
+(8B)</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr"/>
       <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Science
-(9B)</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr"/>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Science
 (8A)</t>
         </is>
       </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Science
+(9A)</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -7273,17 +7303,17 @@
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(8B)</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Science
+(9A)</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Science
-(9A)</t>
+(9B)</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -7317,19 +7347,19 @@
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>Science
+(8B)</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Science
+(9B)</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Science
 (9A)</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(9B)</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(8B)</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -7354,11 +7384,16 @@
 (9A)</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Science
+(8B)</t>
+        </is>
+      </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Science
-(8B)</t>
+(9B)</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -7367,7 +7402,12 @@
 (9B)</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Science
+(8A)</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -7387,19 +7427,19 @@
       <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Science
+(8B)</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Science
 (9B)</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Science
-(9B)</t>
-        </is>
-      </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>Science
-(8B)</t>
+(8A)</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -7427,7 +7467,7 @@
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Science
-(8A)</t>
+(8B)</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -7536,7 +7576,7 @@
       <c r="C3" s="5" t="inlineStr">
         <is>
           <t>IT
-(9A)</t>
+(12)</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -7563,8 +7603,18 @@
 (11)</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr"/>
-      <c r="I3" s="6" t="inlineStr"/>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(9B)</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(9A)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -7581,171 +7631,221 @@
       <c r="C4" s="5" t="inlineStr">
         <is>
           <t>IT
+(10A)</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(10B)</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(10B)</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(9B)</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(11)</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>IT
 (9A)</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(12)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>IT
 (10A)</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(10A)</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>IT
 (10B)</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(11)</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(11)</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>IT
 (9B)</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(9A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(12)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(9A)</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(10A)</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(10B)</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(9B)</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>IT
 (11)</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr"/>
-      <c r="I4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(9A)</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>IT
 (12)</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>IT
 (10A)</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>IT
 (10B)</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>IT
 (9B)</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>IT
 (11)</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr"/>
-      <c r="I5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(9A)</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>IT
 (12)</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>IT
+(9A)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>IT
 (10A)</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>IT
 (10B)</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>IT
-(9A)</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>IT
-(9B)</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr"/>
-      <c r="I6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>IT
-(12)</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>IT
-(10A)</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>IT
-(10B)</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>IT
-(9A)</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>IT
-(11)</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>IT
-(9A)</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
       <c r="F8" s="5" t="inlineStr">
         <is>
           <t>IT
@@ -7849,36 +7949,36 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>English
+Laxmipriya</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Priyanka</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Nandini</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>CS
 Sanjukta</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>English
-Laxmipriya</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Odia
 Ganesh</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Nandini</t>
-        </is>
-      </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Hindi
@@ -7891,12 +7991,7 @@
 Ganesh</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Priyanka</t>
-        </is>
-      </c>
+      <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -7904,229 +7999,234 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>English
+Laxmipriya</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Priyanka</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Nandini</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Ganesh</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Hindi
+Snigdha</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+Ganesh</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>English
+Laxmipriya</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Priyanka</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>CS
 Sanjukta</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Priyanka</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Odia
 Ganesh</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Nandini</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+Ganesh</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>English
+Laxmipriya</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Priyanka</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>CS
+Sanjukta</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>SST
 Srikant</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Math
 Nandini</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>English
+Laxmipriya</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Priyanka</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Nandini</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Ganesh</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Hindi
 Snigdha</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Sanskrit
 Ganesh</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>English
-Laxmipriya</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>CS
 Sanjukta</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>English
+Laxmipriya</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Science
 Priyanka</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>English
-Laxmipriya</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Nandini</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>SST
 Srikant</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Nandini</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-Ganesh</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Priyanka</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Priyanka</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>English
-Laxmipriya</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Nandini</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr"/>
-      <c r="I6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>CS
-Sanjukta</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Priyanka</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>English
-Laxmipriya</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Odia
 Ganesh</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
-Snigdha</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-Ganesh</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Nandini</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>CS
-Sanjukta</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Nandini</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>English
-Laxmipriya</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-Ganesh</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -8294,7 +8394,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H3" s="12" t="inlineStr"/>
       <c r="I3" s="16" t="n">
@@ -8308,7 +8408,7 @@
         <v>6</v>
       </c>
       <c r="M3" s="15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N3" s="12" t="inlineStr"/>
       <c r="O3" s="16" t="n">
@@ -8328,7 +8428,7 @@
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
@@ -8340,7 +8440,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H4" s="12" t="inlineStr"/>
       <c r="I4" s="16" t="n">
@@ -8354,7 +8454,7 @@
         <v>6</v>
       </c>
       <c r="M4" s="15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N4" s="12" t="inlineStr"/>
       <c r="O4" s="16" t="n">
@@ -8386,7 +8486,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5" s="12" t="inlineStr"/>
       <c r="I5" s="16" t="n">
@@ -8400,7 +8500,7 @@
         <v>6</v>
       </c>
       <c r="M5" s="15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N5" s="12" t="inlineStr"/>
       <c r="O5" s="16" t="n">
@@ -8432,7 +8532,7 @@
         <v>2</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6" s="12" t="inlineStr"/>
       <c r="I6" s="16" t="n">
@@ -8446,7 +8546,7 @@
         <v>6</v>
       </c>
       <c r="M6" s="15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N6" s="12" t="inlineStr"/>
       <c r="O6" s="16" t="n">
@@ -8478,7 +8578,7 @@
         <v>2</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H7" s="12" t="inlineStr"/>
       <c r="I7" s="16" t="n">
@@ -8502,7 +8602,7 @@
         <v>4</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
@@ -8524,7 +8624,7 @@
         <v>2</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H8" s="12" t="inlineStr"/>
       <c r="I8" s="16" t="n">
@@ -8576,13 +8676,13 @@
       </c>
       <c r="J9" s="12" t="inlineStr"/>
       <c r="K9" s="15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L9" s="16" t="n">
         <v>7</v>
       </c>
       <c r="M9" s="15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N9" s="12" t="inlineStr"/>
       <c r="O9" s="16" t="n">
@@ -8618,13 +8718,13 @@
       </c>
       <c r="J10" s="12" t="inlineStr"/>
       <c r="K10" s="15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L10" s="16" t="n">
         <v>7</v>
       </c>
       <c r="M10" s="15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N10" s="12" t="inlineStr"/>
       <c r="O10" s="16" t="n">
@@ -8660,13 +8760,13 @@
       </c>
       <c r="J11" s="12" t="inlineStr"/>
       <c r="K11" s="15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L11" s="16" t="n">
         <v>7</v>
       </c>
       <c r="M11" s="15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N11" s="12" t="inlineStr"/>
       <c r="O11" s="16" t="n">
@@ -8674,7 +8774,7 @@
       </c>
       <c r="P11" s="12" t="inlineStr"/>
       <c r="Q11" s="16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -8702,13 +8802,13 @@
       </c>
       <c r="J12" s="12" t="inlineStr"/>
       <c r="K12" s="15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L12" s="16" t="n">
         <v>7</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N12" s="12" t="inlineStr"/>
       <c r="O12" s="16" t="n">
@@ -8726,7 +8826,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
@@ -8748,7 +8848,7 @@
       </c>
       <c r="J13" s="12" t="inlineStr"/>
       <c r="K13" s="15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L13" s="16" t="n">
         <v>7</v>
@@ -8768,7 +8868,7 @@
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
@@ -8790,7 +8890,7 @@
       </c>
       <c r="J14" s="12" t="inlineStr"/>
       <c r="K14" s="15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L14" s="16" t="n">
         <v>7</v>
@@ -8810,7 +8910,7 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
@@ -8830,7 +8930,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
@@ -8840,7 +8940,7 @@
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
@@ -8850,7 +8950,7 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -8948,278 +9048,278 @@
 Ganesh</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>English
+Laxmipriya</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Hindi
+Snigdha</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+Ganesh</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Nandini</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Priyanka</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr"/>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Ganesh</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>English
+Laxmipriya</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Hindi
+Snigdha</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+Ganesh</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Nandini</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Priyanka</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Ganesh</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>English
+Laxmipriya</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Nandini</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+Ganesh</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>CS
 Sanjukta</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Priyanka</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Ganesh</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>English
+Laxmipriya</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Nandini</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+Ganesh</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>CS
+Sanjukta</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Priyanka</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Ganesh</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>English
+Laxmipriya</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Hindi
 Snigdha</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-Ganesh</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>English
-Laxmipriya</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Priyanka</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Math
 Nandini</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-Ganesh</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>CS
 Sanjukta</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Priyanka</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Priyanka</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>English
+Laxmipriya</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Hindi
 Snigdha</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-Ganesh</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>English
-Laxmipriya</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Priyanka</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Math
 Nandini</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>English
-Laxmipriya</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>CS
 Sanjukta</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Nandini</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-Ganesh</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Priyanka</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>English
-Laxmipriya</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>CS
-Sanjukta</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Nandini</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-Ganesh</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Priyanka</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-Ganesh</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>CS
-Sanjukta</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
-Snigdha</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>English
-Laxmipriya</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Nandini</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Priyanka</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-Ganesh</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Priyanka</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
-Snigdha</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>English
-Laxmipriya</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Nandini</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -9339,279 +9439,279 @@
 Ganesh</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Math
+JB</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>SST
+ANIL</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Subhasmita</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr"/>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Hindi
+Snigdha</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+Ganesh</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Math
+JB</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>SST
+ANIL</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Subhasmita</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>CS
 Sanjukta</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>English
 Pratikshya</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Math
+JB</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Hindi
+Snigdha</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>SST
 ANIL</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>CS
+Sanjukta</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>Science
 Sunil</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Math
+JB</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Hindi
 Snigdha</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>SST
+ANIL</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Subhasmita</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>CS
+Sanjukta</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Math
+JB</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Sanskrit
 Ganesh</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>SST
+ANIL</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Subhasmita</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>CS
 Sanjukta</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>SST
-ANIL</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-Subhasmita</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Math
 JB</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sunil</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Sanskrit
 Ganesh</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
-Snigdha</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>CS
-Sanjukta</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>SST
+ANIL</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>English
 Pratikshya</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>SST
-ANIL</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-Subhasmita</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sunil</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-Ganesh</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
-Snigdha</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>CS
-Sanjukta</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>SST
-ANIL</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-Subhasmita</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>SST
-ANIL</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>CS
-Sanjukta</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-Subhasmita</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sunil</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>SST
-ANIL</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sunil</t>
-        </is>
-      </c>
+      <c r="F8" s="6" t="inlineStr"/>
       <c r="G8" s="6" t="inlineStr"/>
       <c r="H8" s="7" t="inlineStr">
         <is>
@@ -9718,24 +9818,24 @@
 JB</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sunil</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>SST
-ANIL</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>SST
+ANIL</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
           <t>CS
@@ -9775,13 +9875,18 @@
 ANIL</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sunil</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>CS
+Sanjukta</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
           <t>English
@@ -9789,12 +9894,7 @@
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
+      <c r="I4" s="6" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -9810,191 +9910,186 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
+          <t>Odia
+Subhasmita</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
           <t>Sanskrit
 Ganesh</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>SST
 ANIL</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Math
+JB</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>CS
+Sanjukta</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Hindi
+Snigdha</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Sanskrit
+Ganesh</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>SST
+ANIL</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Math
+JB</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>CS
 Sanjukta</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sunil</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Hindi
 Snigdha</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Subhasmita</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Sanskrit
 Ganesh</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>SST
 ANIL</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Math
+JB</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Hindi
+Snigdha</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>CS
-Sanjukta</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sunil</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
-Snigdha</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Sanskrit
 Ganesh</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>SST
 ANIL</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-Subhasmita</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>CS
-Sanjukta</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Science
 Sunil</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Hindi
-Snigdha</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Sanskrit
-Ganesh</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>SST
-ANIL</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-Subhasmita</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>CS
-Sanjukta</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -10108,43 +10203,48 @@
 Pratikshya</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Math
+JB</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Math
+JB</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Subhasmita</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>IT
 Usha</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sunil</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -10158,177 +10258,187 @@
 Pratikshya</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Math
+JB</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Subhasmita</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>IT
 Usha</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>English
 Pratikshya</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Math
 JB</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>SST
 Srikant</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Science
 Sunil</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>IT
+Usha</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>English
 Pratikshya</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>IT
+Usha</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>SST
 Srikant</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Math
 JB</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sunil</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sunil</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sunil</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>IT
 Usha</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Math
+JB</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sunil</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>IT
 Usha</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>Odia
-Subhasmita</t>
-        </is>
-      </c>
       <c r="I7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
@@ -10337,22 +10447,22 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>IT
 Usha</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>SST
 Srikant</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -10472,28 +10582,28 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>English
 Pratikshya</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -10504,12 +10614,22 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Science
-Sunil</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr"/>
-      <c r="I3" s="6" t="inlineStr"/>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>IT
+Usha</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Math
+JB</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -10517,28 +10637,28 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>English
-Pratikshya</t>
+          <t>Math
+JB</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -10549,8 +10669,8 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Math
-JB</t>
+          <t>Science
+Sunil</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -10567,43 +10687,48 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Math
 JB</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Math
+JB</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>IT
 Usha</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sunil</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr"/>
       <c r="I5" s="6" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
@@ -10612,42 +10737,42 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Math
 JB</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Math
-JB</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>IT
 Usha</t>
         </is>
       </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sunil</t>
+        </is>
+      </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Science
@@ -10662,34 +10787,34 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>English
+Pratikshya</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
-        </is>
-      </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Math
 JB</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sunil</t>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>IT
+Usha</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -10709,20 +10834,20 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
+          <t>SST
+Srikant</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
           <t>English
 Pratikshya</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>English
-Pratikshya</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>SST
-Srikant</t>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Subhasmita</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -10860,31 +10985,31 @@
 Usha</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Mira</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Science
+Sidharth</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Mira</t>
+        </is>
+      </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Math
-Mira</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
           <t>English
 Laxmipriya</t>
         </is>
       </c>
+      <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -10898,38 +11023,43 @@
 ANIL</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>English
-Laxmipriya</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>IT
 Usha</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Math
 Mira</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr"/>
-      <c r="H4" s="6" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sidharth</t>
-        </is>
-      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>English
+Laxmipriya</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Mira</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>English
+Laxmipriya</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -10943,36 +11073,41 @@
 ANIL</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>English
-Laxmipriya</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>IT
 Usha</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Mira</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>IT
+Usha</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>English
+Laxmipriya</t>
+        </is>
+      </c>
       <c r="G5" s="6" t="inlineStr"/>
-      <c r="H5" s="6" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Mira</t>
+        </is>
+      </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Science
-Sidharth</t>
+          <t>English
+Laxmipriya</t>
         </is>
       </c>
     </row>
@@ -10990,8 +11125,8 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>English
-Laxmipriya</t>
+          <t>Science
+Sidharth</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -11000,31 +11135,26 @@
 Usha</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Mira</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Mira</t>
+        </is>
+      </c>
       <c r="G6" s="6" t="inlineStr"/>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Science
-Sidharth</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sidharth</t>
-        </is>
-      </c>
+          <t>English
+Laxmipriya</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -11040,8 +11170,8 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>English
-Laxmipriya</t>
+          <t>Science
+Sidharth</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -11050,26 +11180,26 @@
 Usha</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Math
-Mira</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Odia
 Subhasmita</t>
         </is>
       </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Math
+Mira</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>Science
-Sidharth</t>
-        </is>
-      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>English
+Laxmipriya</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -11085,26 +11215,26 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>English
-Laxmipriya</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
           <t>Science
 Sidharth</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>IT
+Usha</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Odia
+Subhasmita</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Math
 Mira</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>English
-Laxmipriya</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr"/>
